--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.68455190632203</v>
+        <v>9.861239684777329</v>
       </c>
       <c r="D2" t="n">
-        <v>60.83200638263956</v>
+        <v>9.885201037178929</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F2" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.68745685499661</v>
+        <v>8.39921173893695</v>
       </c>
       <c r="D3" t="n">
-        <v>50.50021399334798</v>
+        <v>8.206284773919048</v>
       </c>
       <c r="E3" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F3" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.29983806286432</v>
+        <v>8.823723685215452</v>
       </c>
       <c r="D4" t="n">
-        <v>55.80087642878534</v>
+        <v>9.067642419677618</v>
       </c>
       <c r="E4" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F4" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.04563489729328</v>
+        <v>8.944915670810158</v>
       </c>
       <c r="D5" t="n">
-        <v>39.74391214543508</v>
+        <v>6.4583857236332</v>
       </c>
       <c r="E5" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F5" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.41773968156146</v>
+        <v>6.892882698253737</v>
       </c>
       <c r="D6" t="n">
-        <v>34.58524091124549</v>
+        <v>5.620101648077392</v>
       </c>
       <c r="E6" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F6" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.59411101760525</v>
+        <v>8.871543040360853</v>
       </c>
       <c r="D7" t="n">
-        <v>30.2255573616637</v>
+        <v>4.911653071270352</v>
       </c>
       <c r="E7" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F7" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.9772193950943</v>
+        <v>3.896298151702824</v>
       </c>
       <c r="D8" t="n">
-        <v>17.09407766159406</v>
+        <v>2.777787620009035</v>
       </c>
       <c r="E8" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F8" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.11987455074463</v>
+        <v>2.131979614496003</v>
       </c>
       <c r="D9" t="n">
-        <v>13.65950803497632</v>
+        <v>2.219670055683652</v>
       </c>
       <c r="E9" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F9" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.40575730894754</v>
+        <v>7.378435562703975</v>
       </c>
       <c r="D10" t="n">
-        <v>47.32510290243454</v>
+        <v>7.690329221645612</v>
       </c>
       <c r="E10" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F10" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.08887862317323</v>
+        <v>2.93944277626565</v>
       </c>
       <c r="D11" t="n">
-        <v>20.64629644953676</v>
+        <v>3.355023173049724</v>
       </c>
       <c r="E11" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F11" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>64.17949340848804</v>
+        <v>10.42916767887931</v>
       </c>
       <c r="D12" t="n">
-        <v>63.22606826282172</v>
+        <v>10.27423609270853</v>
       </c>
       <c r="E12" t="n">
-        <v>16.82894759459495</v>
+        <v>2.734703984121679</v>
       </c>
       <c r="F12" t="n">
-        <v>16.79100697406186</v>
+        <v>2.728538633285052</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
